--- a/110-creation-exemples/ig/StructureDefinition-as-dp-organization.xlsx
+++ b/110-creation-exemples/ig/StructureDefinition-as-dp-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-03T16:21:44+00:00</t>
+    <t>2024-07-01T16:22:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/110-creation-exemples/ig/StructureDefinition-as-dp-organization.xlsx
+++ b/110-creation-exemples/ig/StructureDefinition-as-dp-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-02T08:22:21+00:00</t>
+    <t>2024-07-02T09:45:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/110-creation-exemples/ig/StructureDefinition-as-dp-organization.xlsx
+++ b/110-creation-exemples/ig/StructureDefinition-as-dp-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-02T09:45:37+00:00</t>
+    <t>2024-07-02T11:34:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -789,7 +789,7 @@
 per-1</t>
   </si>
   <si>
-    <t>dateCreation</t>
+    <t>EntiteJuridique.dateCreation</t>
   </si>
   <si>
     <t>DR.1</t>
@@ -819,7 +819,7 @@
     <t>Period.end</t>
   </si>
   <si>
-    <t>dateFermeture</t>
+    <t>EntiteJuridique.dateFermeture</t>
   </si>
   <si>
     <t>DR.2</t>
@@ -860,7 +860,7 @@
     <t>Extension créée dans le cadre de l'Annuaire Santé pour prise en compte de la licence d’exploitation d’une officine.</t>
   </si>
   <si>
-    <t>numeroLicenceOfficine</t>
+    <t>EntiteJuridique.numeroLicenceOfficine</t>
   </si>
   <si>
     <t>Organization.extension:as-ext-organization-pricing-model</t>
@@ -895,7 +895,7 @@
     <t>Extension créée dans le cadre de l'Annuaire Santé pour prise en compte du type de fermeture de la structure.</t>
   </si>
   <si>
-    <t>typeFermeture</t>
+    <t>EntiteJuridique.typeFermeture</t>
   </si>
   <si>
     <t>Organization.extension:as-ext-organization-budget-type</t>
@@ -1179,7 +1179,7 @@
     <t>Identifiant idNat_Struct délivré par une autorité d'enregistrement tel que défini dans l'Annexe Transverse Source des données métier pour les professionnels et les structures.</t>
   </si>
   <si>
-    <t>idNat_struct</t>
+    <t>EntiteJuridique.idNat_struct</t>
   </si>
   <si>
     <t>Organization.identifier:idNatSt.id</t>
@@ -1232,7 +1232,7 @@
     <t>Identifiant SIREN (9 chiffres) ou SIRET (14 chiffres)</t>
   </si>
   <si>
-    <t>numSiren</t>
+    <t>EntiteJuridique.numSiren</t>
   </si>
   <si>
     <t>Organization.identifier:sirene.id</t>
@@ -1482,7 +1482,7 @@
     <t>Identifiant FINESS Entité Géographique (EG) ou Entité Juridique (EJ)</t>
   </si>
   <si>
-    <t>numFiness</t>
+    <t>EntiteJuridique.numFiness</t>
   </si>
   <si>
     <t>Organization.identifier:finess.id</t>
@@ -1968,7 +1968,7 @@
     <t>https://mos.esante.gouv.fr/NOS/JDV_J99-InseeNAFrav2Niveau5-RASS/FHIR/JDV-J99-InseeNAFrav2Niveau5-RASS</t>
   </si>
   <si>
-    <t>codeAPEN</t>
+    <t>EntiteJuridique.codeAPEN</t>
   </si>
   <si>
     <t>Organization.type:activiteINSEE.id</t>
@@ -2010,7 +2010,7 @@
     <t>https://mos.esante.gouv.fr/NOS/JDV_J100-FinessStatutJuridique-RASS/FHIR/JDV-J100-FinessStatutJuridique-RASS</t>
   </si>
   <si>
-    <t>statutJuridique</t>
+    <t>EntiteJuridique.statutJuridique</t>
   </si>
   <si>
     <t>Organization.type:statutJuridiqueINSEE.id</t>
@@ -2130,7 +2130,7 @@
     <t>Need to use the name as the label of the organization.</t>
   </si>
   <si>
-    <t>raisonSociale</t>
+    <t>EntiteJuridique.raisonSociale</t>
   </si>
   <si>
     <t>XON.1</t>
@@ -2158,7 +2158,7 @@
 For searching knowing previous names that the organization was known by can be very useful.</t>
   </si>
   <si>
-    <t>raisonSocialeLongue</t>
+    <t>EntiteJuridique.raisonSocialeLongue</t>
   </si>
   <si>
     <t>Organization.telecom</t>
@@ -2188,7 +2188,7 @@
 ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}org-3:The telecom of an organization can never be of use 'home' {where(use = 'home').empty()}</t>
   </si>
   <si>
-    <t>telecommunication</t>
+    <t>EntiteJuridique.telecommunication</t>
   </si>
   <si>
     <t>XTN</t>
@@ -2643,7 +2643,7 @@
 org-2:An address of an organization can never be of use 'home' {where(use = 'home').empty()}</t>
   </si>
   <si>
-    <t>adresseEJ</t>
+    <t>EntiteJuridique.adresseEJ</t>
   </si>
   <si>
     <t>XAD</t>

--- a/110-creation-exemples/ig/StructureDefinition-as-dp-organization.xlsx
+++ b/110-creation-exemples/ig/StructureDefinition-as-dp-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-02T11:51:09+00:00</t>
+    <t>2024-07-02T12:01:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/110-creation-exemples/ig/StructureDefinition-as-dp-organization.xlsx
+++ b/110-creation-exemples/ig/StructureDefinition-as-dp-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-02T12:01:26+00:00</t>
+    <t>2024-07-02T12:28:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/110-creation-exemples/ig/StructureDefinition-as-dp-organization.xlsx
+++ b/110-creation-exemples/ig/StructureDefinition-as-dp-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-02T12:28:16+00:00</t>
+    <t>2024-07-02T14:06:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/110-creation-exemples/ig/StructureDefinition-as-dp-organization.xlsx
+++ b/110-creation-exemples/ig/StructureDefinition-as-dp-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-02T14:06:23+00:00</t>
+    <t>2024-07-09T09:28:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/110-creation-exemples/ig/StructureDefinition-as-dp-organization.xlsx
+++ b/110-creation-exemples/ig/StructureDefinition-as-dp-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-09T09:28:43+00:00</t>
+    <t>2024-07-09T09:35:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
